--- a/data/trans_bre/IP16A02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-49,31; 2,47</t>
+          <t>-47,26; 2,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 27,58</t>
+          <t>-16,57; 26,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 19,14</t>
+          <t>-24,87; 17,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 18,49</t>
+          <t>-27,4; 17,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,76; 4,98</t>
+          <t>-73,21; 13,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 159,09</t>
+          <t>-41,18; 138,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,76; 102,0</t>
+          <t>-62,8; 91,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,35; 37,82</t>
+          <t>-38,2; 35,46</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 21,91</t>
+          <t>-26,35; 25,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 21,38</t>
+          <t>-32,18; 19,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 22,05</t>
+          <t>-27,3; 21,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 25,3</t>
+          <t>-23,01; 25,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,71; 81,23</t>
+          <t>-49,26; 92,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,4; 79,05</t>
+          <t>-52,28; 72,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,46; 68,73</t>
+          <t>-49,82; 65,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 81,97</t>
+          <t>-39,1; 79,2</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 36,38</t>
+          <t>-20,12; 38,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 17,21</t>
+          <t>-36,59; 17,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-46,31; 21,28</t>
+          <t>-47,52; 18,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 41,84</t>
+          <t>-18,65; 47,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 155,65</t>
+          <t>-46,97; 180,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,65; 35,46</t>
+          <t>-50,07; 33,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,04; 58,79</t>
+          <t>-68,28; 51,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,27; 172,0</t>
+          <t>-43,45; 204,66</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 6,66</t>
+          <t>-29,24; 6,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 17,35</t>
+          <t>-10,95; 16,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 23,47</t>
+          <t>-8,17; 24,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,83; 11,02</t>
+          <t>-36,25; 11,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,23; 18,64</t>
+          <t>-54,35; 18,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 62,42</t>
+          <t>-27,07; 64,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 100,15</t>
+          <t>-18,39; 101,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,04; 31,04</t>
+          <t>-76,27; 31,95</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 16,22</t>
+          <t>-28,52; 17,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 21,45</t>
+          <t>-19,62; 20,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 27,25</t>
+          <t>-11,71; 24,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 30,51</t>
+          <t>-11,62; 30,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-63,62; 58,61</t>
+          <t>-62,91; 66,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 64,23</t>
+          <t>-35,41; 61,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 123,31</t>
+          <t>-26,43; 113,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 101,19</t>
+          <t>-24,52; 109,2</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 41,94</t>
+          <t>-29,08; 45,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 69,46</t>
+          <t>12,93; 68,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,78; 16,57</t>
+          <t>-41,74; 18,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 33,66</t>
+          <t>-31,3; 34,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,78; 315,11</t>
+          <t>-71,62; 367,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,01; 595,03</t>
+          <t>25,03; 492,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-79,01; 107,22</t>
+          <t>-82,34; 154,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,69; 141,7</t>
+          <t>-52,16; 148,0</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 3,22</t>
+          <t>-16,43; 3,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 12,2</t>
+          <t>-4,87; 12,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 10,6</t>
+          <t>-8,04; 10,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 8,49</t>
+          <t>-21,42; 8,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 8,43</t>
+          <t>-35,05; 11,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 33,1</t>
+          <t>-11,3; 33,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 34,46</t>
+          <t>-18,83; 33,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-43,16; 19,93</t>
+          <t>-43,43; 20,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 2,47</t>
+          <t>-48,06; 2,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 26,43</t>
+          <t>-16,51; 27,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 17,74</t>
+          <t>-25,24; 18,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,4; 17,45</t>
+          <t>-28,18; 17,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,21; 13,28</t>
+          <t>-73,38; 5,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 138,84</t>
+          <t>-40,73; 157,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 91,61</t>
+          <t>-62,08; 103,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 35,46</t>
+          <t>-38,57; 36,89</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 25,18</t>
+          <t>-26,14; 24,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 19,76</t>
+          <t>-31,92; 20,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 21,57</t>
+          <t>-27,5; 21,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 25,41</t>
+          <t>-25,7; 25,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,26; 92,43</t>
+          <t>-51,76; 97,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,28; 72,65</t>
+          <t>-51,62; 73,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,82; 65,28</t>
+          <t>-50,18; 66,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 79,2</t>
+          <t>-43,0; 76,19</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 38,05</t>
+          <t>-18,7; 37,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 17,39</t>
+          <t>-37,9; 15,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-47,52; 18,39</t>
+          <t>-42,6; 22,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 47,4</t>
+          <t>-25,62; 44,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,97; 180,48</t>
+          <t>-45,23; 170,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,07; 33,97</t>
+          <t>-51,5; 30,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 51,91</t>
+          <t>-63,45; 73,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,45; 204,66</t>
+          <t>-46,61; 211,81</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 6,26</t>
+          <t>-29,45; 5,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 16,96</t>
+          <t>-11,61; 16,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 24,99</t>
+          <t>-8,89; 22,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 11,81</t>
+          <t>-40,93; 10,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,35; 18,11</t>
+          <t>-54,99; 17,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 64,23</t>
+          <t>-26,77; 59,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 101,46</t>
+          <t>-21,45; 90,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,27; 31,95</t>
+          <t>-74,24; 27,89</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 17,15</t>
+          <t>-30,37; 16,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 20,9</t>
+          <t>-18,93; 20,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 24,83</t>
+          <t>-13,2; 26,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 30,46</t>
+          <t>-11,7; 29,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 66,75</t>
+          <t>-66,06; 64,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 61,05</t>
+          <t>-35,06; 58,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 113,43</t>
+          <t>-29,84; 124,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 109,2</t>
+          <t>-24,39; 101,6</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 45,49</t>
+          <t>-26,28; 44,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,93; 68,09</t>
+          <t>9,45; 68,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 18,62</t>
+          <t>-41,99; 15,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 34,69</t>
+          <t>-31,21; 32,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,62; 367,88</t>
+          <t>-70,72; 449,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,03; 492,9</t>
+          <t>21,24; 539,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,34; 154,45</t>
+          <t>-81,21; 99,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,16; 148,0</t>
+          <t>-54,03; 137,37</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 3,63</t>
+          <t>-16,42; 3,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 12,11</t>
+          <t>-4,94; 12,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 10,54</t>
+          <t>-6,8; 10,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 8,42</t>
+          <t>-22,71; 9,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 11,69</t>
+          <t>-35,25; 9,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 33,0</t>
+          <t>-10,99; 33,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 33,04</t>
+          <t>-16,14; 31,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 20,23</t>
+          <t>-47,17; 21,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,48</t>
+          <t>-5,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-7,34%</t>
+          <t>-8,22%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 2,24</t>
+          <t>-49,31; 2,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 27,72</t>
+          <t>-16,02; 27,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 18,65</t>
+          <t>-26,57; 19,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,18; 17,98</t>
+          <t>-27,36; 19,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,38; 5,45</t>
+          <t>-75,76; 4,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 157,96</t>
+          <t>-38,99; 159,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,08; 103,56</t>
+          <t>-64,76; 102,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 36,89</t>
+          <t>-38,88; 38,19</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 24,37</t>
+          <t>-27,52; 21,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 20,08</t>
+          <t>-30,45; 21,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 21,97</t>
+          <t>-28,0; 22,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 25,46</t>
+          <t>-22,47; 26,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,76; 97,06</t>
+          <t>-49,71; 81,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 73,25</t>
+          <t>-51,4; 79,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,18; 66,94</t>
+          <t>-51,46; 68,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 76,19</t>
+          <t>-39,84; 88,25</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,7</t>
+          <t>14,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 37,86</t>
+          <t>-19,81; 36,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-37,9; 15,89</t>
+          <t>-37,93; 17,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 22,51</t>
+          <t>-46,31; 21,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 44,3</t>
+          <t>-17,84; 43,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 170,49</t>
+          <t>-50,89; 155,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,5; 30,87</t>
+          <t>-51,65; 35,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,45; 73,46</t>
+          <t>-70,04; 58,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 211,81</t>
+          <t>-33,42; 184,43</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-11,58</t>
+          <t>8,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-28,77%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 5,79</t>
+          <t>-28,9; 6,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 16,7</t>
+          <t>-10,97; 17,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 22,56</t>
+          <t>-9,05; 23,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,93; 10,85</t>
+          <t>-9,74; 25,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,99; 17,76</t>
+          <t>-55,23; 18,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 59,31</t>
+          <t>-26,13; 62,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 90,35</t>
+          <t>-22,59; 100,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,24; 27,89</t>
+          <t>-21,39; 86,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 16,2</t>
+          <t>-29,71; 16,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 20,1</t>
+          <t>-16,98; 21,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 26,35</t>
+          <t>-11,85; 27,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 29,31</t>
+          <t>-13,34; 29,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-66,06; 64,54</t>
+          <t>-63,62; 58,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 58,83</t>
+          <t>-32,56; 64,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 124,95</t>
+          <t>-28,91; 123,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 101,6</t>
+          <t>-29,18; 95,55</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 44,24</t>
+          <t>-28,09; 41,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,45; 68,73</t>
+          <t>6,74; 69,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 15,77</t>
+          <t>-40,78; 16,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,21; 32,85</t>
+          <t>-32,93; 35,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 449,05</t>
+          <t>-74,78; 315,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,24; 539,42</t>
+          <t>14,01; 595,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,21; 99,93</t>
+          <t>-79,01; 107,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,03; 137,37</t>
+          <t>-56,75; 140,31</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,53</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-7,96%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 3,52</t>
+          <t>-16,66; 3,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 12,6</t>
+          <t>-5,38; 12,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 10,08</t>
+          <t>-7,05; 10,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 9,48</t>
+          <t>-4,29; 15,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-35,25; 9,63</t>
+          <t>-36,83; 8,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 33,72</t>
+          <t>-12,19; 33,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 31,16</t>
+          <t>-17,06; 34,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 21,73</t>
+          <t>-8,83; 40,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-24,44</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,45</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,94</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,04</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-43,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-9,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-8,22%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-7.74462173514055</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.737157679455841</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.401624053993949</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.029052606936892</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.6268261257476865</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1428586614792774</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1307859070892956</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.07090636834146916</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-49,31; 2,47</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-16,02; 27,58</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-26,57; 19,14</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-27,36; 19,06</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-75,76; 4,98</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-38,99; 159,09</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-64,76; 102,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-38,88; 38,19</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-15.12411587530276</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.090287864109254</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.8152140804662</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.802933261509931</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.8721847879092428</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8147559403786842</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.845431305484557</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4794430601449831</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-2.134073997494888</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.662049647437935</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.692380038850754</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.507680627184625</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>-0.1686492871475317</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.22382748457869</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3.728653523304226</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.7274424549492418</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-5,86</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,25</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-2,61%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-12,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-4,94%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-27,52; 21,91</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-30,45; 21,38</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-28,0; 22,05</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-22,47; 26,74</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-49,71; 81,23</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-51,4; 79,05</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-51,46; 68,73</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-39,84; 88,25</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.3651153322302148</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.6045096892405</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-5.604374855715959</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.005229598283672254</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04251275781173842</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.8432694440949235</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.9121626902774708</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.0004535647066940704</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8,99</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-9,94</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-13,83</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-15,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-24,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.413808123917458</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.038209870430487</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-9.969763516802196</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-8.051628981004502</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5603074020301185</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3678083620798345</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5592223702693637</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-19,81; 36,38</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-37,93; 17,21</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-46,31; 21,28</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-17,84; 43,79</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-50,89; 155,65</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-51,65; 35,46</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-70,04; 58,79</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-33,42; 184,43</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.121893235643591</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.21451464189612</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-2.488899034572121</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.680757709269752</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.522854198019423</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>5.000682470471968</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>-0.2875247478884358</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.9914301173335048</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-11,6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,42</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,36</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,82</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-25,86%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.3792719096462269</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.266145986468873</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.563721809228192</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.8574793613957341</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.05178466907883656</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3535514286508654</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.5343329110097153</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.08256580409144595</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-28,9; 6,66</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-10,97; 17,35</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-9,05; 23,47</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-9,74; 25,71</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-55,23; 18,64</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-26,13; 62,42</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-22,59; 100,15</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-21,39; 86,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.218826588160327</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.382480700815822</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-9.61152554383531</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.475619848174713</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6432196915153056</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.8353845428534596</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.9058037597239866</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6309468212677587</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.534852059970018</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.499316908442487</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.236183723281878</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.757367722072245</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.585956095417525</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.20303508214521</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.304746082631382</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.380308174565362</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-8,21</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,37</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,91</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-21,19%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>22,37%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-29,71; 16,22</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-16,98; 21,45</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-11,85; 27,25</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-13,34; 29,55</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-63,62; 58,61</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-32,56; 64,23</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-28,91; 123,31</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-29,18; 95,55</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-2.366739318447454</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1200411517052184</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3.525418932625526</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.779883189201982</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2749137929918538</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.02227231752473597</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1.250562162191054</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1918594248539284</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>5,66</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>42,21</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-11,01</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>145,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-31,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-7.219692049995271</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.474231628969207</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.3952827377797999</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.405022216527827</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6524475023613902</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4897995606266299</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.01187546612233941</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2849730258003357</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-28,09; 41,94</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>6,74; 69,46</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-40,78; 16,57</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-32,93; 35,48</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-74,78; 315,11</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>14,01; 595,03</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-79,01; 107,22</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-56,75; 140,31</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.428625061193959</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.892517114761703</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.762627905494877</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.526512152468166</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2498706071018075</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.04328915738945</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>4.265956336979076</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.8537058365363128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,289 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-7,07</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,68</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-16,87%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-1.744659890693319</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.3131906333792921</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.2559460252044912</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>3.201223191765412</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2399023156495548</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.05267279758756284</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.07096516491912208</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.3657325352024561</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-16,66; 3,22</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-5,38; 12,2</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-7,05; 10,6</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-4,29; 15,96</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-36,83; 8,43</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-12,19; 33,1</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-17,06; 34,46</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-8,83; 40,74</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-6.739565984852631</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.75799479418727</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.525179036168508</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.764297384481718</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7302504151026618</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.5717147862092635</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6480231733108234</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2610333484609065</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3.814048718911474</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.200523678159256</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.078520728902387</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>10.11634067915066</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.8268913055431469</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.223269612015399</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.360845709591376</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.886439817220487</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-1.086842769088876</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1.988404405036693</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2.275514976312787</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-0.9387412691425137</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.2379405262441057</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.4141653914018745</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.8122351481125164</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.1041243576465708</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-6.596212834286462</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-4.448198883494744</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-2.912817047264623</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-9.93036152609108</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="n">
+        <v>-0.7613587312565107</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="n">
+        <v>-0.7636219557551289</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>4.256955414552412</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>9.360473036166182</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>8.055825902005578</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>6.944438140694649</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="n">
+        <v>4.716739809943022</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="n">
+        <v>1.717119393924173</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-2.29724535245921</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.2646051028505035</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.1095995333280107</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.7771795044843294</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.2775154058736454</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.04915531517314911</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.02775139633962453</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.07432874807496076</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-4.27905392715924</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.88725612336248</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.6219740457962</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-2.081858267618823</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.4666881045904733</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2965841789378523</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.3531594959035702</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.1762419884345227</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.1080367089793392</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.229374985345867</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.709426754437415</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.701769922052576</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.01562916512919118</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.5110649849543017</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.5399150595113325</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.4149216164007022</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1309,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
